--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97DE6C87-A012-4202-A178-5A38E104C715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9C4934B-909D-4D70-B057-129C6C28141E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37980" yWindow="-3180" windowWidth="6285" windowHeight="7665" xr2:uid="{075366E4-FC0C-4C8D-B110-A4A9C4D64A5C}"/>
+    <workbookView xWindow="37470" yWindow="-3690" windowWidth="6285" windowHeight="7665" xr2:uid="{E9DD18D2-5740-4B4C-867D-0FA2194B1462}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="3">
   <si>
-    <t>checking uploader</t>
+    <t>test test test test</t>
   </si>
   <si>
     <t>n</t>
@@ -396,7 +396,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E79D962B-25E7-4AEF-8750-ED64663EAE73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E4D78F-CCA2-4A55-B8C2-DBE4AA4E1D8D}">
   <dimension ref="A2:H66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
